--- a/AGIO.xlsx
+++ b/AGIO.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Martin Shkreli - DL\models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4DCE97A0-6D66-4F8D-8CF3-FFCAD7BBA304}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8EC59968-CCF0-40FF-8AEE-AFEBC0C3A497}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11170" yWindow="880" windowWidth="23470" windowHeight="16810" xr2:uid="{8C49F58B-8EDA-4FF2-8C57-4A5AE93FFE34}"/>
+    <workbookView xWindow="15790" yWindow="1850" windowWidth="22360" windowHeight="13710" xr2:uid="{8C49F58B-8EDA-4FF2-8C57-4A5AE93FFE34}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -56,7 +56,7 @@
     <t>EV</t>
   </si>
   <si>
-    <t>Q325</t>
+    <t>Q126</t>
   </si>
 </sst>
 </file>
@@ -451,7 +451,7 @@
         <v>0</v>
       </c>
       <c r="J2" s="2">
-        <v>23</v>
+        <v>32</v>
       </c>
     </row>
     <row r="3" spans="9:11" x14ac:dyDescent="0.25">
@@ -459,7 +459,7 @@
         <v>1</v>
       </c>
       <c r="J3" s="3">
-        <v>58.313811999999999</v>
+        <v>58.781999999999996</v>
       </c>
       <c r="K3" s="4" t="s">
         <v>6</v>
@@ -471,7 +471,7 @@
       </c>
       <c r="J4" s="3">
         <f>+J2*J3</f>
-        <v>1341.217676</v>
+        <v>1881.0239999999999</v>
       </c>
     </row>
     <row r="5" spans="9:11" x14ac:dyDescent="0.25">
@@ -479,8 +479,7 @@
         <v>3</v>
       </c>
       <c r="J5" s="3">
-        <f>92.71+860.15+304.341</f>
-        <v>1257.201</v>
+        <v>1000</v>
       </c>
       <c r="K5" s="4" t="s">
         <v>6</v>
@@ -503,7 +502,7 @@
       </c>
       <c r="J7" s="3">
         <f>+J4-J5+J6</f>
-        <v>84.016675999999961</v>
+        <v>881.02399999999989</v>
       </c>
     </row>
   </sheetData>
